--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\JIENG_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882F0F23-F8EC-4842-992E-BBEA45B6722F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E0222F-7EF7-432F-8F50-46B206BD94DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Time (4)" sheetId="9" r:id="rId3"/>
     <sheet name="Time (3)" sheetId="8" r:id="rId4"/>
     <sheet name="Time" sheetId="5" r:id="rId5"/>
-    <sheet name="Time (2)" sheetId="7" r:id="rId6"/>
+    <sheet name="Family" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,17 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\JIENG_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E0222F-7EF7-432F-8F50-46B206BD94DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACFC890-6DBE-4495-B73B-6DF45E094613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
   </bookViews>
   <sheets>
-    <sheet name="Time (6)" sheetId="11" r:id="rId1"/>
-    <sheet name="Time (5)" sheetId="10" r:id="rId2"/>
-    <sheet name="Time (4)" sheetId="9" r:id="rId3"/>
-    <sheet name="Time (3)" sheetId="8" r:id="rId4"/>
+    <sheet name="Domestic Animals" sheetId="14" r:id="rId1"/>
+    <sheet name="Time (6)" sheetId="11" r:id="rId2"/>
+    <sheet name="Time (5)" sheetId="10" r:id="rId3"/>
+    <sheet name="Family" sheetId="7" r:id="rId4"/>
     <sheet name="Time" sheetId="5" r:id="rId5"/>
-    <sheet name="Family" sheetId="7" r:id="rId6"/>
+    <sheet name="Greetings and Dialogue" sheetId="8" r:id="rId6"/>
+    <sheet name="Shapes" sheetId="9" r:id="rId7"/>
+    <sheet name="Plants" sheetId="17" r:id="rId8"/>
+    <sheet name="Disease" sheetId="16" r:id="rId9"/>
+    <sheet name="Insects" sheetId="15" r:id="rId10"/>
+    <sheet name="Numbers" sheetId="12" r:id="rId11"/>
+    <sheet name="Wild Animals" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="39">
   <si>
     <t>English_Text</t>
   </si>
@@ -90,6 +96,63 @@
   </si>
   <si>
     <t>Faternal Auntie</t>
+  </si>
+  <si>
+    <t>Abel_Audio_Speaker</t>
+  </si>
+  <si>
+    <t>Maternal Grandpa</t>
+  </si>
+  <si>
+    <t>Faternal Grandpa</t>
+  </si>
+  <si>
+    <t>Maternal Grandma</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>One o'clock</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Night</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Prepe</t>
+  </si>
+  <si>
+    <t>Downs</t>
+  </si>
+  <si>
+    <t>Supper</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Dinner</t>
   </si>
 </sst>
 </file>
@@ -440,6 +503,186 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85ED16D2-8534-48C7-98FC-264467A89D38}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A194AA10-EE15-418F-9DAE-0B2E567D1AD2}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0C41F3-1D4B-497E-825C-C61507F272F6}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526FEE9F-F006-46E2-9587-EB822B23477C}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C085786-EE2D-4816-8C1B-F806B63813E6}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -484,7 +727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B39DE55-EEC3-4D32-8F3B-7A7BE8FCFCB6}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -529,7 +772,297 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E460CF8-30D8-48CC-9E34-ADA0AB344E63}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C74CD01-FD58-4A3E-AE7F-CFCDE8943688}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8C4766-3845-4299-B15E-A1699F745F79}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816B4540-3B65-497F-8548-309251C8E089}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -574,8 +1107,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8C4766-3845-4299-B15E-A1699F745F79}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FFB63D-C4FE-4B7C-AC11-80ECA4885B28}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -619,8 +1152,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C74CD01-FD58-4A3E-AE7F-CFCDE8943688}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801803F5-4B44-40A8-AD90-4FBCADBA0272}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -662,109 +1195,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E460CF8-30D8-48CC-9E34-ADA0AB344E63}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\JIENG_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACFC890-6DBE-4495-B73B-6DF45E094613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7A834D-D46E-4DC3-9486-78EC10490D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
   </bookViews>
@@ -20,11 +20,13 @@
     <sheet name="Time" sheetId="5" r:id="rId5"/>
     <sheet name="Greetings and Dialogue" sheetId="8" r:id="rId6"/>
     <sheet name="Shapes" sheetId="9" r:id="rId7"/>
-    <sheet name="Plants" sheetId="17" r:id="rId8"/>
-    <sheet name="Disease" sheetId="16" r:id="rId9"/>
-    <sheet name="Insects" sheetId="15" r:id="rId10"/>
-    <sheet name="Numbers" sheetId="12" r:id="rId11"/>
-    <sheet name="Wild Animals" sheetId="13" r:id="rId12"/>
+    <sheet name="Proffestionals" sheetId="19" r:id="rId8"/>
+    <sheet name="Car Spares" sheetId="18" r:id="rId9"/>
+    <sheet name="Plants" sheetId="17" r:id="rId10"/>
+    <sheet name="Disease" sheetId="16" r:id="rId11"/>
+    <sheet name="Insects" sheetId="15" r:id="rId12"/>
+    <sheet name="Numbers" sheetId="12" r:id="rId13"/>
+    <sheet name="Wild Animals" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="39">
   <si>
     <t>English_Text</t>
   </si>
@@ -548,7 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A194AA10-EE15-418F-9DAE-0B2E567D1AD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FFB63D-C4FE-4B7C-AC11-80ECA4885B28}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -593,7 +595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0C41F3-1D4B-497E-825C-C61507F272F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801803F5-4B44-40A8-AD90-4FBCADBA0272}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -638,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526FEE9F-F006-46E2-9587-EB822B23477C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A194AA10-EE15-418F-9DAE-0B2E567D1AD2}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -682,8 +684,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C085786-EE2D-4816-8C1B-F806B63813E6}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0C41F3-1D4B-497E-825C-C61507F272F6}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -727,8 +729,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B39DE55-EEC3-4D32-8F3B-7A7BE8FCFCB6}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526FEE9F-F006-46E2-9587-EB822B23477C}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -772,6 +774,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C085786-EE2D-4816-8C1B-F806B63813E6}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B39DE55-EEC3-4D32-8F3B-7A7BE8FCFCB6}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E460CF8-30D8-48CC-9E34-ADA0AB344E63}">
   <dimension ref="A1:H17"/>
@@ -1108,7 +1200,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FFB63D-C4FE-4B7C-AC11-80ECA4885B28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57954954-B3F2-463A-A951-B0EBB1263FE2}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1153,7 +1245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801803F5-4B44-40A8-AD90-4FBCADBA0272}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDEF9E9-E4CF-4E4C-A08D-9DC30CE12982}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\JIENG_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7A834D-D46E-4DC3-9486-78EC10490D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED7E822-46AE-492C-83B4-C8C19E297B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="16" xr2:uid="{733DA877-3F38-4053-9643-52AB18D24183}"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic Animals" sheetId="14" r:id="rId1"/>
-    <sheet name="Time (6)" sheetId="11" r:id="rId2"/>
-    <sheet name="Time (5)" sheetId="10" r:id="rId3"/>
+    <sheet name="Farming" sheetId="11" r:id="rId2"/>
+    <sheet name="Grazing" sheetId="10" r:id="rId3"/>
     <sheet name="Family" sheetId="7" r:id="rId4"/>
     <sheet name="Time" sheetId="5" r:id="rId5"/>
     <sheet name="Greetings and Dialogue" sheetId="8" r:id="rId6"/>
@@ -27,6 +27,9 @@
     <sheet name="Insects" sheetId="15" r:id="rId12"/>
     <sheet name="Numbers" sheetId="12" r:id="rId13"/>
     <sheet name="Wild Animals" sheetId="13" r:id="rId14"/>
+    <sheet name="Mathematis signs" sheetId="21" r:id="rId15"/>
+    <sheet name="Colors" sheetId="22" r:id="rId16"/>
+    <sheet name="Parts of the Body" sheetId="23" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>English_Text</t>
   </si>
@@ -76,12 +79,6 @@
     <t>Parent</t>
   </si>
   <si>
-    <t>Son/Boy</t>
-  </si>
-  <si>
-    <t>Daughter?Girl</t>
-  </si>
-  <si>
     <t>Brother</t>
   </si>
   <si>
@@ -155,6 +152,150 @@
   </si>
   <si>
     <t>Dinner</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>Daughter</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Substract</t>
+  </si>
+  <si>
+    <t>Multiply</t>
+  </si>
+  <si>
+    <t>Divide</t>
+  </si>
+  <si>
+    <t>Equal</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Nave blue</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Thigh</t>
+  </si>
+  <si>
+    <t>Leg</t>
+  </si>
+  <si>
+    <t>Groin</t>
+  </si>
+  <si>
+    <t>Waist</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>Cheek</t>
+  </si>
+  <si>
+    <t>Heel</t>
+  </si>
+  <si>
+    <t>Toe</t>
+  </si>
+  <si>
+    <t>Elbow</t>
+  </si>
+  <si>
+    <t>Ankle</t>
+  </si>
+  <si>
+    <t>knee</t>
+  </si>
+  <si>
+    <t>Knee cap</t>
+  </si>
+  <si>
+    <t>Shin</t>
+  </si>
+  <si>
+    <t>Toes</t>
+  </si>
+  <si>
+    <t>Soles</t>
+  </si>
+  <si>
+    <t>Calf</t>
+  </si>
+  <si>
+    <t>Index figure</t>
+  </si>
+  <si>
+    <t>Thumb</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>Ring</t>
+  </si>
+  <si>
+    <t>Hair</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>eyelahes</t>
+  </si>
+  <si>
+    <t>nose</t>
   </si>
 </sst>
 </file>
@@ -774,6 +915,371 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A1F0A38-311A-4316-8341-363E097A5780}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6D11E8-ED8F-451B-8372-A1BD30B39D42}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CDCD8A-C8C8-4643-A7C6-7AAA20C1B833}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C085786-EE2D-4816-8C1B-F806B63813E6}">
   <dimension ref="A1:H1"/>
@@ -866,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E460CF8-30D8-48CC-9E34-ADA0AB344E63}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -892,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -916,72 +1422,82 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1031,77 +1547,77 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
